--- a/tables/Datas/param.xlsx
+++ b/tables/Datas/param.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java\sunrise-game-frame\tables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375" tabRatio="500"/>
   </bookViews>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>##column#var</t>
   </si>
@@ -77,12 +82,6 @@
   </si>
   <si>
     <t>新角色初始化地图id</t>
-  </si>
-  <si>
-    <t>GMCmdStatus</t>
-  </si>
-  <si>
-    <t>gm指令开启状态</t>
   </si>
   <si>
     <t>DefaultHeadIcon</t>
@@ -1131,8 +1130,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
     <col min="2" max="3" width="22.125" style="1" customWidth="1"/>
@@ -1238,23 +1237,6 @@
         <v>17</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1">
         <v>1001</v>
       </c>
     </row>
